--- a/artfynd/A 35430-2024 artfynd.xlsx
+++ b/artfynd/A 35430-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115166534</v>
+        <v>115166537</v>
       </c>
       <c r="B2" t="n">
-        <v>56481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Malånäset, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720189</v>
+        <v>720090</v>
       </c>
       <c r="R2" t="n">
-        <v>7218242</v>
+        <v>7218264</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -784,12 +775,7 @@
         <v>115166538</v>
       </c>
       <c r="B3" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,6 +870,314 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115166534</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Malånäset, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>720189</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7218242</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122466738</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vargfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>719966</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7218310</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jennifer Sondell, Torun Bergman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115166535</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Malånäset, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>720148</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7218257</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
